--- a/libraries/unit-test/unit-test.xlsx
+++ b/libraries/unit-test/unit-test.xlsx
@@ -397,654 +397,643 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:H26"/>
+  <cols>
+    <col min="1" max="1" width="26.6640625" customWidth="1"/>
+    <col min="2" max="2" width="26.6640625" customWidth="1"/>
+    <col min="3" max="3" width="86.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10.00390625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="20.00390625" customWidth="1"/>
+    <col min="8" max="8" width="20.00390625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>module</v>
+        <v>Function</v>
       </c>
       <c r="B1" t="str">
-        <v>test</v>
+        <v>Test Case ID</v>
       </c>
       <c r="C1" t="str">
-        <v>status</v>
+        <v>Test Case Title</v>
       </c>
       <c r="D1" t="str">
-        <v>duration</v>
+        <v>Pre-conditions</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Test Step</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Expected Result</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Actual Result</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Test Automation?</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>EasyFormAction</v>
+        <v>admin-user</v>
       </c>
       <c r="B2" t="str">
+        <v>UserInfo</v>
+      </c>
+      <c r="C2" t="str">
         <v>renders correctly</v>
       </c>
-      <c r="C2" t="str">
-        <v>passed</v>
-      </c>
       <c r="D2" t="str">
-        <v>333.66</v>
+        <v/>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>EasyFormAction</v>
+        <v>admin-user</v>
       </c>
       <c r="B3" t="str">
-        <v>handles add action correctly</v>
+        <v>UserInfo</v>
       </c>
       <c r="C3" t="str">
-        <v>passed</v>
+        <v>handles user edit</v>
       </c>
       <c r="D3" t="str">
-        <v>217.98</v>
+        <v/>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>EasyFormAction</v>
+        <v>admin-user</v>
       </c>
       <c r="B4" t="str">
-        <v>handles action command correctly</v>
+        <v>UserInfo</v>
       </c>
       <c r="C4" t="str">
-        <v>passed</v>
+        <v>handles password change dialog</v>
       </c>
       <c r="D4" t="str">
-        <v>249.63</v>
+        <v/>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>EasyFormDesigner</v>
+        <v>admin-user</v>
       </c>
       <c r="B5" t="str">
-        <v>should render correctly when loading fields</v>
+        <v>UserInfo</v>
       </c>
       <c r="C5" t="str">
-        <v>passed</v>
+        <v>confirms user deletion and deletes user</v>
       </c>
       <c r="D5" t="str">
-        <v>38.48</v>
+        <v/>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>EasyFormDesigner</v>
+        <v>admin-user</v>
       </c>
       <c r="B6" t="str">
-        <v>should call handleSubmit and show success message</v>
+        <v>UserInfo</v>
       </c>
       <c r="C6" t="str">
-        <v>passed</v>
+        <v>does not delete user if confirmation is canceled</v>
       </c>
       <c r="D6" t="str">
-        <v>10.00</v>
+        <v/>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>EasyFormDesigner</v>
+        <v>admin-user</v>
       </c>
       <c r="B7" t="str">
-        <v>should handle submit error</v>
+        <v>UserInfo</v>
       </c>
       <c r="C7" t="str">
-        <v>passed</v>
+        <v>sets user status correctly</v>
       </c>
       <c r="D7" t="str">
-        <v>517.04</v>
+        <v/>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>EasyFormDesigner</v>
+        <v>admin-user</v>
       </c>
       <c r="B8" t="str">
-        <v>should handle field list correctly</v>
+        <v>UserInfo</v>
       </c>
       <c r="C8" t="str">
-        <v>passed</v>
+        <v>handles status update failure</v>
       </c>
       <c r="D8" t="str">
-        <v>10.39</v>
+        <v/>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>EasyFormDesigner</v>
+        <v>admin-user</v>
       </c>
       <c r="B9" t="str">
-        <v>should get detail and update state correctly</v>
+        <v>AdminUserList</v>
       </c>
       <c r="C9" t="str">
-        <v>passed</v>
+        <v>renders correctly</v>
       </c>
       <c r="D9" t="str">
-        <v>10.45</v>
+        <v/>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>EasyFormDetail</v>
+        <v>admin-user</v>
       </c>
       <c r="B10" t="str">
-        <v>should render the component correctly</v>
+        <v>AdminUserList</v>
       </c>
       <c r="C10" t="str">
-        <v>passed</v>
+        <v>handles filter change correctly</v>
       </c>
       <c r="D10" t="str">
-        <v>16.05</v>
+        <v/>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>EasyFormDetail</v>
+        <v>admin-user</v>
       </c>
       <c r="B11" t="str">
-        <v>should fetch detail and call handleEmailUpdate</v>
+        <v>AdminUserList</v>
       </c>
       <c r="C11" t="str">
-        <v>passed</v>
+        <v>opens user detail correctly</v>
       </c>
       <c r="D11" t="str">
-        <v>7.83</v>
+        <v/>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>EasyFormDetail</v>
+        <v>admin-user</v>
       </c>
       <c r="B12" t="str">
-        <v>should handle errors correctly</v>
+        <v>UserTable</v>
       </c>
       <c r="C12" t="str">
-        <v>passed</v>
+        <v>renders correctly</v>
       </c>
       <c r="D12" t="str">
-        <v>5.87</v>
+        <v/>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>EasyFormDetail</v>
+        <v>admin-user</v>
       </c>
       <c r="B13" t="str">
-        <v>should update action correctly</v>
+        <v>UserTable</v>
       </c>
       <c r="C13" t="str">
-        <v>passed</v>
+        <v>fetches user count on mount</v>
       </c>
       <c r="D13" t="str">
-        <v>3.52</v>
+        <v/>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>EasyFormDetail</v>
+        <v>admin-user</v>
       </c>
       <c r="B14" t="str">
-        <v>should delete action correctly</v>
+        <v>UserTable</v>
       </c>
       <c r="C14" t="str">
-        <v>passed</v>
+        <v>handles user deletion confirmation</v>
       </c>
       <c r="D14" t="str">
-        <v>4.12</v>
+        <v/>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>EasyFormDetail</v>
+        <v>admin-user</v>
       </c>
       <c r="B15" t="str">
-        <v>should call handleEmailUpdate and reload logRef</v>
+        <v>UserTable</v>
       </c>
       <c r="C15" t="str">
-        <v>passed</v>
+        <v>does not delete users if confirmation is canceled</v>
       </c>
       <c r="D15" t="str">
-        <v>2.88</v>
+        <v/>
       </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>EasyFormDetail</v>
+        <v>admin-user</v>
       </c>
       <c r="B16" t="str">
-        <v>should fetch detail correctly</v>
+        <v>UserTable</v>
       </c>
       <c r="C16" t="str">
-        <v>passed</v>
+        <v>sets user status correctly</v>
       </c>
       <c r="D16" t="str">
-        <v>7.36</v>
+        <v/>
       </c>
       <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>EasyFormEmailLog</v>
+        <v>admin-user</v>
       </c>
       <c r="B17" t="str">
-        <v>renders correctly</v>
+        <v>UserTable</v>
       </c>
       <c r="C17" t="str">
-        <v>passed</v>
+        <v>shows warning when active users exceed license limit</v>
       </c>
       <c r="D17" t="str">
-        <v>5.35</v>
+        <v/>
       </c>
       <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>EasyFormEmailLog</v>
+        <v>admin-user</v>
       </c>
       <c r="B18" t="str">
-        <v>initializes filter conditions</v>
+        <v>UserTable</v>
       </c>
       <c r="C18" t="str">
-        <v>passed</v>
+        <v>handles filter form change</v>
       </c>
       <c r="D18" t="str">
-        <v>1.70</v>
+        <v/>
       </c>
       <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>EasyFormEmailLog</v>
+        <v>admin-user</v>
       </c>
       <c r="B19" t="str">
-        <v>calls handleOpenCase when case tag is clicked</v>
+        <v>UserTable</v>
       </c>
       <c r="C19" t="str">
-        <v>passed</v>
+        <v>clears filters correctly</v>
       </c>
       <c r="D19" t="str">
-        <v>0.35</v>
+        <v/>
       </c>
       <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>EasyFormEmailLog</v>
+        <v>admin-user</v>
       </c>
       <c r="B20" t="str">
-        <v>updates table on email update</v>
+        <v>AdminUserDetail</v>
       </c>
       <c r="C20" t="str">
-        <v>passed</v>
+        <v>renders correctly</v>
       </c>
       <c r="D20" t="str">
-        <v>0.35</v>
+        <v/>
       </c>
       <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>EasyFormEmailLog</v>
+        <v>admin-user</v>
       </c>
       <c r="B21" t="str">
-        <v>handles filter form change correctly</v>
+        <v>AdminUserDetail</v>
       </c>
       <c r="C21" t="str">
-        <v>passed</v>
+        <v>opens user list correctly</v>
       </c>
       <c r="D21" t="str">
-        <v>0.45</v>
+        <v/>
       </c>
       <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>EasyFormDetailName</v>
+        <v>admin-user</v>
       </c>
       <c r="B22" t="str">
-        <v>should render the component correctly</v>
+        <v>AdminUserDetail</v>
       </c>
       <c r="C22" t="str">
-        <v>passed</v>
+        <v>handles user data retrieval correctly</v>
       </c>
       <c r="D22" t="str">
-        <v>41.66</v>
+        <v/>
       </c>
       <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>EasyFormDetailName</v>
+        <v>admin-user</v>
       </c>
       <c r="B23" t="str">
-        <v>initializes form with detail name</v>
+        <v>AdminUserDetail</v>
       </c>
       <c r="C23" t="str">
-        <v>passed</v>
+        <v>does not set user data if no data is returned</v>
       </c>
       <c r="D23" t="str">
-        <v>9.58</v>
+        <v/>
       </c>
       <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>EasyFormDetailName</v>
-      </c>
-      <c r="B24" t="str">
-        <v>handles name change correctly</v>
-      </c>
-      <c r="C24" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D24" t="str">
-        <v>12.64</v>
-      </c>
-      <c r="E24" t="str">
-        <v/>
+        <v>Total</v>
+      </c>
+      <c r="B24">
+        <v>22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>EasyFormDetailName</v>
-      </c>
-      <c r="B25" t="str">
-        <v>publishes correctly</v>
-      </c>
-      <c r="C25" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D25" t="str">
-        <v>10.06</v>
-      </c>
-      <c r="E25" t="str">
-        <v/>
+        <v>Passed</v>
+      </c>
+      <c r="B25">
+        <v>21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>EasyFormDetailName</v>
-      </c>
-      <c r="B26" t="str">
-        <v>watches for detail changes</v>
-      </c>
-      <c r="C26" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D26" t="str">
-        <v>10.39</v>
-      </c>
-      <c r="E26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>EasyFormDetailName</v>
-      </c>
-      <c r="B27" t="str">
-        <v>handles error during name change</v>
-      </c>
-      <c r="C27" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D27" t="str">
-        <v>9.58</v>
-      </c>
-      <c r="E27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>EasyFormPage</v>
-      </c>
-      <c r="B28" t="str">
-        <v>should render the component correctly</v>
-      </c>
-      <c r="C28" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D28" t="str">
-        <v>372.04</v>
-      </c>
-      <c r="E28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>EasyFormPage</v>
-      </c>
-      <c r="B29" t="str">
-        <v>should call handleAdd when button is clicked</v>
-      </c>
-      <c r="C29" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D29" t="str">
-        <v>230.50</v>
-      </c>
-      <c r="E29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>EasyFormPage</v>
-      </c>
-      <c r="B30" t="str">
-        <v>should call handleDblclick with correct row</v>
-      </c>
-      <c r="C30" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D30" t="str">
-        <v>258.24</v>
-      </c>
-      <c r="E30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>EasyFormPage</v>
-      </c>
-      <c r="B31" t="str">
-        <v>should activate and deactivate correctly</v>
-      </c>
-      <c r="C31" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D31" t="str">
-        <v>194.89</v>
-      </c>
-      <c r="E31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>EasyFormPage</v>
-      </c>
-      <c r="B32" t="str">
-        <v>should call handleFilterFormChange with correct parameters</v>
-      </c>
-      <c r="C32" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D32" t="str">
-        <v>212.95</v>
-      </c>
-      <c r="E32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>EasyFormDetailName</v>
-      </c>
-      <c r="B33" t="str">
-        <v>should render the component correctly</v>
-      </c>
-      <c r="C33" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D33" t="str">
-        <v>70.22</v>
-      </c>
-      <c r="E33" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>EasyFormDetailName</v>
-      </c>
-      <c r="B34" t="str">
-        <v>initializes form with detail name</v>
-      </c>
-      <c r="C34" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D34" t="str">
-        <v>14.98</v>
-      </c>
-      <c r="E34" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>EasyFormDetailName</v>
-      </c>
-      <c r="B35" t="str">
-        <v>handles name change correctly</v>
-      </c>
-      <c r="C35" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D35" t="str">
-        <v>18.21</v>
-      </c>
-      <c r="E35" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>EasyFormDetailName</v>
-      </c>
-      <c r="B36" t="str">
-        <v>publishes correctly</v>
-      </c>
-      <c r="C36" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D36" t="str">
-        <v>16.58</v>
-      </c>
-      <c r="E36" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>EasyFormDetailName</v>
-      </c>
-      <c r="B37" t="str">
-        <v>watches for detail changes</v>
-      </c>
-      <c r="C37" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D37" t="str">
-        <v>16.44</v>
-      </c>
-      <c r="E37" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>EasyFormDetailName</v>
-      </c>
-      <c r="B38" t="str">
-        <v>handles error during name change</v>
-      </c>
-      <c r="C38" t="str">
-        <v>passed</v>
-      </c>
-      <c r="D38" t="str">
-        <v>11.20</v>
-      </c>
-      <c r="E38" t="str">
-        <v/>
+        <v>Failed</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H26"/>
   </ignoredErrors>
 </worksheet>
 </file>